--- a/config/swarm-disaster-generated/templates/SwarmDisasterContent.xlsx
+++ b/config/swarm-disaster-generated/templates/SwarmDisasterContent.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="199">
   <si>
     <t>@table</t>
   </si>
@@ -278,7 +278,7 @@
     <t>SwarmDisasterCurioState</t>
   </si>
   <si>
-    <t>4215d98c289a66ec</t>
+    <t>0feaa41a08b707bc</t>
   </si>
   <si>
     <t>curio_id</t>
@@ -293,7 +293,7 @@
     <t>lifecycle_json</t>
   </si>
   <si>
-    <t>repair_target</t>
+    <t>repair_target_json</t>
   </si>
   <si>
     <t>ref&lt;SwarmDisasterCurio.id&gt;</t>
@@ -410,7 +410,7 @@
     <t>SwarmDisasterService</t>
   </si>
   <si>
-    <t>280c533b17c923ac</t>
+    <t>0fc2163a83977ca3</t>
   </si>
   <si>
     <t>shared_service_id</t>
@@ -1560,7 +1560,8 @@
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="17.7109375" style="5" customWidth="1"/>
-    <col min="17" max="18" width="12.7109375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="16.7109375" style="5" customWidth="1"/>
     <col min="19" max="19" width="26.7109375" style="5" customWidth="1"/>
     <col min="20" max="20" width="23.7109375" style="5" customWidth="1"/>
     <col min="21" max="21" width="22.7109375" style="5" customWidth="1"/>
@@ -1802,13 +1803,13 @@
         <v>38</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>42</v>
@@ -1943,15 +1944,9 @@
       <c r="Q6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="R6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
       <c r="U6" s="5" t="s">
         <v>51</v>
       </c>
@@ -6289,7 +6284,7 @@
     <col min="19" max="19" width="16.7109375" style="5" customWidth="1"/>
     <col min="20" max="20" width="19.7109375" style="5" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="5" customWidth="1"/>
-    <col min="22" max="22" width="16.7109375" style="5" customWidth="1"/>
+    <col min="22" max="22" width="18.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -6525,7 +6520,7 @@
         <v>38</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -6650,7 +6645,9 @@
       <c r="U6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="V6" s="5"/>
+      <c r="V6" s="5" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="7" spans="1:22" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
